--- a/बजेट माग estimate/thekka/kerabaari khanepaani/केराबारी खानेपानी - sir.xlsx
+++ b/बजेट माग estimate/thekka/kerabaari khanepaani/केराबारी खानेपानी - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88198FC2-EF2C-4B67-B1C1-8E3A43EC1EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45BD0AE-FA88-4221-A1A5-8C6325809E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$64</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -124,24 +124,9 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
-    <t>User contribution</t>
-  </si>
-  <si>
     <t>Length (m)</t>
   </si>
   <si>
@@ -166,9 +151,6 @@
     <t>Location:- Shankharapur Municipality 1</t>
   </si>
   <si>
-    <t>-13% VAT for material</t>
-  </si>
-  <si>
     <t>-for pipe laying</t>
   </si>
   <si>
@@ -208,18 +190,9 @@
     <t>-for stand taps</t>
   </si>
   <si>
-    <t>-13% VAT for sand</t>
-  </si>
-  <si>
     <t>Plain cement concrete (1:2:4)</t>
   </si>
   <si>
-    <t>-13% VAT for cement</t>
-  </si>
-  <si>
-    <t>-13% VAT for aggregate</t>
-  </si>
-  <si>
     <t>sqm</t>
   </si>
   <si>
@@ -254,12 +227,6 @@
   </si>
   <si>
     <t>20mm GI pipe threaded-Medium class</t>
-  </si>
-  <si>
-    <t>-13% VAT</t>
-  </si>
-  <si>
-    <t>-13% VAT for block stone</t>
   </si>
   <si>
     <t>R.R. masonry in 1:6 cement mortar</t>
@@ -481,7 +448,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -593,6 +560,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -602,33 +587,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1156,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="3" customWidth="1"/>
@@ -1174,113 +1132,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
+      <c r="A6" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
+      <c r="H6" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="A7" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="H7" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -1319,10 +1277,10 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="8"/>
@@ -1339,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -1354,7 +1312,7 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
@@ -1380,7 +1338,7 @@
     <row r="12" spans="1:11" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="41" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" s="12">
         <v>1</v>
@@ -1406,7 +1364,7 @@
     <row r="13" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="42" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" s="24"/>
       <c r="D13" s="1"/>
@@ -1417,14 +1375,15 @@
         <v>35.1</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I13" s="2">
-        <v>963.05</v>
+        <f>1.15*963.05</f>
+        <v>1107.5074999999999</v>
       </c>
       <c r="J13" s="43">
         <f>G13*I13</f>
-        <v>33803.055</v>
+        <v>38873.513249999996</v>
       </c>
       <c r="K13" s="15"/>
     </row>
@@ -1446,7 +1405,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -1461,7 +1420,7 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C16" s="11">
         <v>1</v>
@@ -1484,7 +1443,7 @@
     <row r="17" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="42" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="1"/>
@@ -1495,15 +1454,15 @@
         <v>200</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I17" s="2">
-        <f>4308.15/1000</f>
-        <v>4.3081499999999995</v>
+        <f>1.15*4308.15/1000</f>
+        <v>4.9543724999999998</v>
       </c>
       <c r="J17" s="43">
         <f>G17*I17</f>
-        <v>861.62999999999988</v>
+        <v>990.87450000000001</v>
       </c>
       <c r="K17" s="15"/>
     </row>
@@ -1525,17 +1484,17 @@
         <v>3</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
@@ -1620,7 +1579,7 @@
         <v>35.1</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I22" s="2">
         <v>287</v>
@@ -1633,9 +1592,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="16" t="s">
-        <v>35</v>
-      </c>
+      <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -1643,115 +1600,114 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
-      <c r="J23" s="17">
-        <f>0.13*J22</f>
-        <v>1309.5810000000001</v>
-      </c>
+      <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-    </row>
-    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="9"/>
+    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>4</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
-        <v>4</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="11">
+        <v>2</v>
+      </c>
+      <c r="D26" s="22">
+        <v>1.93</v>
+      </c>
+      <c r="E26" s="22">
+        <v>1.93</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="G26" s="22">
+        <f>PRODUCT(C26:F26)</f>
+        <v>1.11747</v>
+      </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="11">
-        <v>2</v>
-      </c>
-      <c r="D27" s="22">
-        <v>1.93</v>
-      </c>
-      <c r="E27" s="22">
-        <v>1.93</v>
-      </c>
-      <c r="F27" s="11">
-        <v>0.15</v>
-      </c>
-      <c r="G27" s="22">
-        <f>PRODUCT(C27:F27)</f>
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14"/>
+      <c r="B27" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="2">
+        <f>SUM(G26)</f>
         <v>1.11747</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-      <c r="B28" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="2">
-        <f>SUM(G27)</f>
-        <v>1.11747</v>
-      </c>
-      <c r="H28" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="2">
-        <f>4493.69</f>
-        <v>4493.6899999999996</v>
-      </c>
-      <c r="J28" s="17">
-        <f>G28*I28</f>
-        <v>5021.5637642999991</v>
-      </c>
-      <c r="K28" s="15"/>
+      <c r="H27" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="2">
+        <f>1.15*4493.69</f>
+        <v>5167.7434999999996</v>
+      </c>
+      <c r="J27" s="17">
+        <f>G27*I27</f>
+        <v>5774.7983289449994</v>
+      </c>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="16" t="s">
-        <v>66</v>
+      <c r="A29" s="10">
+        <v>5</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -1760,170 +1716,205 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
-      <c r="J29" s="17">
-        <f>0.13*G28*3091.19</f>
-        <v>449.06057160899996</v>
-      </c>
+      <c r="J29" s="11"/>
       <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
+      <c r="B30" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C26</f>
+        <v>2</v>
+      </c>
+      <c r="D30" s="22">
+        <f>D26</f>
+        <v>1.93</v>
+      </c>
+      <c r="E30" s="22">
+        <f>E26</f>
+        <v>1.93</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="22">
+        <f>PRODUCT(C30:F30)</f>
+        <v>0.74497999999999998</v>
+      </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
-        <v>5</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="24"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="2">
+        <f>SUM(G30)</f>
+        <v>0.74497999999999998</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="2">
+        <f>1.15*13343.7</f>
+        <v>15345.254999999999</v>
+      </c>
+      <c r="J31" s="17">
+        <f>G31*I31</f>
+        <v>11431.908069899999</v>
+      </c>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
-      <c r="B32" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="11">
-        <f>C27</f>
-        <v>2</v>
-      </c>
-      <c r="D32" s="22">
-        <f>D27</f>
-        <v>1.93</v>
-      </c>
-      <c r="E32" s="22">
-        <f>E27</f>
-        <v>1.93</v>
-      </c>
-      <c r="F32" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="G32" s="22">
-        <f>PRODUCT(C32:F32)</f>
-        <v>0.74497999999999998</v>
-      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
     </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="2">
-        <f>SUM(G32)</f>
-        <v>0.74497999999999998</v>
-      </c>
-      <c r="H33" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="I33" s="2">
-        <v>13343.7</v>
-      </c>
-      <c r="J33" s="17">
-        <f>G33*I33</f>
-        <v>9940.7896259999998</v>
-      </c>
-      <c r="K33" s="15"/>
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
+        <v>6</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="C34" s="11">
+        <f>C26*2</f>
+        <v>4</v>
+      </c>
+      <c r="D34" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="E34" s="22">
+        <v>0.35</v>
+      </c>
+      <c r="F34" s="22">
+        <v>0.6</v>
+      </c>
+      <c r="G34" s="22">
+        <f>PRODUCT(C34:F34)</f>
+        <v>1.008</v>
+      </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="17">
-        <f>0.13*G33*1413.27</f>
-        <v>136.87152499800001</v>
-      </c>
+      <c r="J34" s="11"/>
       <c r="K34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="C35" s="11">
+        <f>C26</f>
+        <v>2</v>
+      </c>
+      <c r="D35" s="22">
+        <v>1.47</v>
+      </c>
+      <c r="E35" s="22">
+        <v>0.35</v>
+      </c>
+      <c r="F35" s="22">
+        <v>0.6</v>
+      </c>
+      <c r="G35" s="22">
+        <f>PRODUCT(C35:F35)</f>
+        <v>0.61739999999999995</v>
+      </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
-      <c r="J35" s="17">
-        <f>0.13*G33*4096</f>
-        <v>396.6869504</v>
-      </c>
+      <c r="J35" s="11"/>
       <c r="K35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="B36" s="16" t="str">
+        <f>B30</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C26</f>
+        <v>2</v>
+      </c>
+      <c r="D36" s="22">
+        <v>0.45</v>
+      </c>
+      <c r="E36" s="22">
+        <v>0.35</v>
+      </c>
+      <c r="F36" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="G36" s="22">
+        <f>PRODUCT(C36:F36)</f>
+        <v>0.378</v>
+      </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
-      <c r="J36" s="17">
-        <f>0.13*G33*(368.76+737.51+1743.21)</f>
-        <v>275.96472935200001</v>
-      </c>
+      <c r="J36" s="11"/>
       <c r="K36" s="11"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
-        <v>6</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>67</v>
-      </c>
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14"/>
+      <c r="B37" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="2">
+        <f>SUM(G34:G36)</f>
+        <v>2.0034000000000001</v>
+      </c>
+      <c r="H37" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="2">
+        <f>1.15*12225.55</f>
+        <v>14059.382499999998</v>
+      </c>
+      <c r="J37" s="17">
+        <f>G37*I37</f>
+        <v>28166.566900499998</v>
+      </c>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -1935,27 +1926,17 @@
       <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="11">
-        <f>C27*2</f>
-        <v>4</v>
-      </c>
-      <c r="D39" s="22">
-        <v>1.2</v>
-      </c>
-      <c r="E39" s="22">
-        <v>0.35</v>
-      </c>
-      <c r="F39" s="22">
-        <v>0.6</v>
-      </c>
-      <c r="G39" s="22">
-        <f>PRODUCT(C39:F39)</f>
-        <v>1.008</v>
-      </c>
+      <c r="A39" s="10">
+        <v>7</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
@@ -1963,25 +1944,25 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="16" t="s">
-        <v>55</v>
+      <c r="B40" s="16" t="str">
+        <f>B34</f>
+        <v>-for wing walls of stand tap</v>
       </c>
       <c r="C40" s="11">
-        <f>C27</f>
-        <v>2</v>
+        <f>C26*4</f>
+        <v>8</v>
       </c>
       <c r="D40" s="22">
-        <v>1.47</v>
-      </c>
-      <c r="E40" s="22">
-        <v>0.35</v>
-      </c>
+        <f>D34</f>
+        <v>1.2</v>
+      </c>
+      <c r="E40" s="22"/>
       <c r="F40" s="22">
         <v>0.6</v>
       </c>
       <c r="G40" s="22">
         <f>PRODUCT(C40:F40)</f>
-        <v>0.61739999999999995</v>
+        <v>5.76</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
@@ -1991,97 +1972,109 @@
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="B41" s="16" t="str">
-        <f>B32</f>
-        <v>-for stand tap</v>
+        <f>B35</f>
+        <v>-for side wall of stand tap</v>
       </c>
       <c r="C41" s="11">
-        <f>C27</f>
+        <f>C26</f>
         <v>2</v>
       </c>
       <c r="D41" s="22">
-        <v>0.45</v>
-      </c>
-      <c r="E41" s="22">
-        <v>0.35</v>
-      </c>
+        <f>D35</f>
+        <v>1.47</v>
+      </c>
+      <c r="E41" s="22"/>
       <c r="F41" s="22">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="G41" s="22">
         <f>PRODUCT(C41:F41)</f>
-        <v>0.378</v>
+        <v>1.764</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
     </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
-      <c r="B42" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="2">
-        <f>SUM(G39:G41)</f>
-        <v>2.0034000000000001</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="I42" s="2">
-        <v>12225.55</v>
-      </c>
-      <c r="J42" s="17">
-        <f>G42*I42</f>
-        <v>24492.666870000001</v>
-      </c>
-      <c r="K42" s="15"/>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="16" t="str">
+        <f>B36</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C42" s="11">
+        <f>C26</f>
+        <v>2</v>
+      </c>
+      <c r="D42" s="22">
+        <f>D36</f>
+        <v>0.45</v>
+      </c>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="G42" s="22">
+        <f>PRODUCT(C42:F42)</f>
+        <v>1.08</v>
+      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="11">
+        <f>C42</f>
+        <v>2</v>
+      </c>
+      <c r="D43" s="22">
+        <v>0.71</v>
+      </c>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22">
+        <v>0.6</v>
+      </c>
+      <c r="G43" s="22">
+        <f>PRODUCT(C43:F43)</f>
+        <v>0.85199999999999998</v>
+      </c>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="17">
-        <f>0.13*G42*1492.66</f>
-        <v>388.75135572000005</v>
-      </c>
+      <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="24"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="2">
+        <f>SUM(G40:G43)</f>
+        <v>9.4559999999999995</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="2">
+        <f>1.15*49954.32/100</f>
+        <v>574.47467999999992</v>
+      </c>
       <c r="J44" s="17">
-        <f>0.13*G42*1356.8</f>
-        <v>353.36770560000002</v>
-      </c>
-      <c r="K44" s="11"/>
+        <f>G44*I44</f>
+        <v>5432.2325740799988</v>
+      </c>
+      <c r="K44" s="15"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="16" t="s">
-        <v>66</v>
-      </c>
+      <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
@@ -2089,15 +2082,16 @@
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
-      <c r="J45" s="17">
-        <f>0.13*G42*2833.59</f>
-        <v>737.98584678000009</v>
-      </c>
+      <c r="J45" s="11"/>
       <c r="K45" s="11"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="10">
+        <v>7</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>53</v>
+      </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -2109,17 +2103,28 @@
       <c r="K46" s="11"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
-        <v>7</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="16" t="str">
+        <f t="shared" ref="B47:D49" si="0">B40</f>
+        <v>-for wing walls of stand tap</v>
+      </c>
+      <c r="C47" s="11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D47" s="22">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22">
+        <f>F40</f>
+        <v>0.6</v>
+      </c>
+      <c r="G47" s="22">
+        <f>PRODUCT(C47:F47)</f>
+        <v>5.76</v>
+      </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
@@ -2128,24 +2133,25 @@
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
       <c r="B48" s="16" t="str">
-        <f>B39</f>
-        <v>-for wing walls of stand tap</v>
+        <f t="shared" si="0"/>
+        <v>-for side wall of stand tap</v>
       </c>
       <c r="C48" s="11">
-        <f>C27*4</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="D48" s="22">
-        <f>D39</f>
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>1.47</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22">
+        <f>F41</f>
         <v>0.6</v>
       </c>
       <c r="G48" s="22">
         <f>PRODUCT(C48:F48)</f>
-        <v>5.76</v>
+        <v>1.764</v>
       </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
@@ -2155,24 +2161,25 @@
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
       <c r="B49" s="16" t="str">
-        <f>B40</f>
-        <v>-for side wall of stand tap</v>
+        <f t="shared" si="0"/>
+        <v>-for stand tap</v>
       </c>
       <c r="C49" s="11">
-        <f>C27</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D49" s="22">
-        <f>D40</f>
-        <v>1.47</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22">
-        <v>0.6</v>
+        <f>F42</f>
+        <v>1.2</v>
       </c>
       <c r="G49" s="22">
         <f>PRODUCT(C49:F49)</f>
-        <v>1.764</v>
+        <v>1.08</v>
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
@@ -2181,25 +2188,23 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="16" t="str">
-        <f>B41</f>
-        <v>-for stand tap</v>
-      </c>
+      <c r="B50" s="16"/>
       <c r="C50" s="11">
-        <f>C27</f>
+        <f>C43</f>
         <v>2</v>
       </c>
       <c r="D50" s="22">
-        <f>D41</f>
-        <v>0.45</v>
+        <f>D43</f>
+        <v>0.71</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22">
-        <v>1.2</v>
+        <f>F43</f>
+        <v>0.6</v>
       </c>
       <c r="G50" s="22">
         <f>PRODUCT(C50:F50)</f>
-        <v>1.08</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
@@ -2208,21 +2213,23 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="16"/>
+      <c r="B51" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="C51" s="11">
-        <f>C50</f>
+        <f>C26</f>
         <v>2</v>
       </c>
       <c r="D51" s="22">
-        <v>0.71</v>
-      </c>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22">
-        <v>0.6</v>
-      </c>
+        <v>1.93</v>
+      </c>
+      <c r="E51" s="22">
+        <v>1.93</v>
+      </c>
+      <c r="F51" s="22"/>
       <c r="G51" s="22">
         <f>PRODUCT(C51:F51)</f>
-        <v>0.85199999999999998</v>
+        <v>7.4497999999999998</v>
       </c>
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
@@ -2239,27 +2246,25 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="2">
-        <f>SUM(G48:G51)</f>
-        <v>9.4559999999999995</v>
+        <f>SUM(G47:G51)</f>
+        <v>16.905799999999999</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I52" s="2">
-        <f>49954.32/100</f>
-        <v>499.54320000000001</v>
+        <f>1.15*28609.6/100</f>
+        <v>329.01039999999995</v>
       </c>
       <c r="J52" s="17">
         <f>G52*I52</f>
-        <v>4723.6804991999998</v>
+        <v>5562.184020319999</v>
       </c>
       <c r="K52" s="15"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="16" t="s">
-        <v>49</v>
-      </c>
+      <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
@@ -2267,16 +2272,15 @@
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
-      <c r="J53" s="17">
-        <f>0.13*G52*7463.32/100</f>
-        <v>91.745100095999987</v>
-      </c>
+      <c r="J53" s="11"/>
       <c r="K53" s="11"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
-      <c r="B54" s="16" t="s">
-        <v>51</v>
+    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="10">
+        <v>8</v>
+      </c>
+      <c r="B54" s="40" t="s">
+        <v>55</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
@@ -2285,517 +2289,196 @@
       <c r="G54" s="11"/>
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
-      <c r="J54" s="17">
-        <f>0.13*G52*7296/100</f>
-        <v>89.688268799999989</v>
-      </c>
+      <c r="J54" s="11"/>
       <c r="K54" s="11"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
+      <c r="B55" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="11">
+        <f>C26</f>
+        <v>2</v>
+      </c>
+      <c r="D55" s="22">
+        <v>1.2</v>
+      </c>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
+      <c r="G55" s="22">
+        <f>PRODUCT(C55:F55)</f>
+        <v>2.4</v>
+      </c>
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
+      <c r="J55" s="17"/>
       <c r="K55" s="11"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="10">
-        <v>7</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
+    <row r="56" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="14"/>
+      <c r="B56" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" s="24"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="43">
+        <f>SUM(G55:G55)</f>
+        <v>2.4</v>
+      </c>
+      <c r="H56" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="2">
+        <f>248</f>
+        <v>248</v>
+      </c>
+      <c r="J56" s="43">
+        <f>G56*I56</f>
+        <v>595.19999999999993</v>
+      </c>
+      <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10"/>
-      <c r="B57" s="16" t="str">
-        <f>B48</f>
-        <v>-for wing walls of stand tap</v>
-      </c>
-      <c r="C57" s="11">
-        <f>C48</f>
-        <v>8</v>
-      </c>
-      <c r="D57" s="22">
-        <f>D48</f>
-        <v>1.2</v>
-      </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22">
-        <f>F48</f>
-        <v>0.6</v>
-      </c>
-      <c r="G57" s="22">
-        <f>PRODUCT(C57:F57)</f>
-        <v>5.76</v>
-      </c>
+      <c r="B57" s="40"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
-      <c r="B58" s="16" t="str">
-        <f>B49</f>
-        <v>-for side wall of stand tap</v>
-      </c>
-      <c r="C58" s="11">
-        <f>C49</f>
-        <v>2</v>
-      </c>
-      <c r="D58" s="22">
-        <f>D49</f>
-        <v>1.47</v>
-      </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22">
-        <f>F49</f>
-        <v>0.6</v>
-      </c>
-      <c r="G58" s="22">
+    <row r="58" spans="1:11" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="14">
+        <v>9</v>
+      </c>
+      <c r="B58" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="24">
+        <v>1</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="43">
         <f>PRODUCT(C58:F58)</f>
-        <v>1.764</v>
-      </c>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H58" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I58" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J58" s="43">
+        <f>G58*I58</f>
+        <v>3000</v>
+      </c>
+      <c r="K58" s="15"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10"/>
-      <c r="B59" s="16" t="str">
-        <f>B50</f>
-        <v>-for stand tap</v>
-      </c>
-      <c r="C59" s="11">
-        <f>C50</f>
-        <v>2</v>
-      </c>
-      <c r="D59" s="22">
-        <f>D50</f>
-        <v>0.45</v>
-      </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22">
-        <f>F50</f>
-        <v>1.2</v>
-      </c>
-      <c r="G59" s="22">
-        <f>PRODUCT(C59:F59)</f>
-        <v>1.08</v>
-      </c>
+      <c r="B59" s="40"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="11">
-        <f>C51</f>
-        <v>2</v>
-      </c>
-      <c r="D60" s="22">
-        <f>D51</f>
-        <v>0.71</v>
-      </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22">
-        <f>F51</f>
-        <v>0.6</v>
-      </c>
-      <c r="G60" s="22">
+    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="14">
+        <v>10</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="24">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="25">
         <f>PRODUCT(C60:F60)</f>
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H60" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="2">
+        <v>500</v>
+      </c>
+      <c r="J60" s="25">
+        <f>G60*I60</f>
+        <v>500</v>
+      </c>
+      <c r="K60" s="15"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="B61" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="11">
-        <f>C27</f>
-        <v>2</v>
-      </c>
-      <c r="D61" s="22">
-        <v>1.93</v>
-      </c>
-      <c r="E61" s="22">
-        <v>1.93</v>
-      </c>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22">
-        <f>PRODUCT(C61:F61)</f>
-        <v>7.4497999999999998</v>
-      </c>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-    </row>
-    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="14"/>
-      <c r="B62" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="2">
-        <f>SUM(G57:G61)</f>
-        <v>16.905799999999999</v>
-      </c>
-      <c r="H62" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="I62" s="2">
-        <f>28609.6/100</f>
-        <v>286.096</v>
-      </c>
+      <c r="A61" s="14"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="15"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="29"/>
+      <c r="B62" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="31"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
       <c r="J62" s="17">
-        <f>G62*I62</f>
-        <v>4836.6817567999997</v>
-      </c>
-      <c r="K62" s="15"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="10"/>
-      <c r="B63" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="17">
-        <f>0.13*G62*6809.6/100</f>
-        <v>149.658256384</v>
-      </c>
-      <c r="K63" s="11"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="10"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-    </row>
-    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
-        <v>8</v>
-      </c>
-      <c r="B65" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="10"/>
-      <c r="B66" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C66" s="11">
-        <f>C27</f>
-        <v>2</v>
-      </c>
-      <c r="D66" s="22">
-        <v>1.2</v>
-      </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="22">
-        <f>PRODUCT(C66:F66)</f>
-        <v>2.4</v>
-      </c>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="11"/>
-    </row>
-    <row r="67" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
-      <c r="B67" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" s="24"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="43">
-        <f>SUM(G66:G66)</f>
-        <v>2.4</v>
-      </c>
-      <c r="H67" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="I67" s="2">
-        <v>248</v>
-      </c>
-      <c r="J67" s="43">
-        <f>G67*I67</f>
-        <v>595.19999999999993</v>
-      </c>
-      <c r="K67" s="15"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="10"/>
-      <c r="B68" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="17">
-        <f>0.13*J67</f>
-        <v>77.375999999999991</v>
-      </c>
-      <c r="K68" s="11"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="10"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="11"/>
-    </row>
-    <row r="70" spans="1:11" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="14">
-        <v>9</v>
-      </c>
-      <c r="B70" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C70" s="24">
-        <v>1</v>
-      </c>
-      <c r="D70" s="1"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="43">
-        <f>PRODUCT(C70:F70)</f>
-        <v>1</v>
-      </c>
-      <c r="H70" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I70" s="2">
-        <v>3000</v>
-      </c>
-      <c r="J70" s="43">
-        <f>G70*I70</f>
-        <v>3000</v>
-      </c>
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="10"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-    </row>
-    <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14">
-        <v>10</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="24">
-        <v>1</v>
-      </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="25">
-        <f>PRODUCT(C72:F72)</f>
-        <v>1</v>
-      </c>
-      <c r="H72" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I72" s="2">
-        <v>500</v>
-      </c>
-      <c r="J72" s="25">
-        <f>G72*I72</f>
-        <v>500</v>
-      </c>
-      <c r="K72" s="15"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="15"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="29"/>
-      <c r="B74" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="31"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17">
-        <f>SUM(J10:J72)</f>
-        <v>102305.70482603899</v>
-      </c>
-      <c r="K74" s="33"/>
-    </row>
-    <row r="76" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="34"/>
-      <c r="B76" s="12" t="s">
+        <f>SUM(J10:J60)</f>
+        <v>110400.97764374498</v>
+      </c>
+      <c r="K62" s="33"/>
+    </row>
+    <row r="64" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="34"/>
+      <c r="B64" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="45">
-        <f>J74</f>
-        <v>102305.70482603899</v>
-      </c>
-      <c r="D76" s="46"/>
-      <c r="E76" s="35">
-        <v>100</v>
-      </c>
-      <c r="F76" s="34"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="34"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="39"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B77" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C77" s="49">
-        <v>90000</v>
-      </c>
-      <c r="D77" s="50"/>
-      <c r="E77" s="35"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B78" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C78" s="49">
-        <f>C77-C80-C81</f>
-        <v>85500</v>
-      </c>
-      <c r="D78" s="50"/>
-      <c r="E78" s="35">
-        <f>C78/C76*100</f>
-        <v>83.573052104361651</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B79" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C79" s="51">
-        <f>C76-C78</f>
-        <v>16805.704826038986</v>
-      </c>
-      <c r="D79" s="51"/>
-      <c r="E79" s="35">
-        <f>100-E78</f>
-        <v>16.426947895638349</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B80" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" s="45">
-        <f>C77*0.03</f>
-        <v>2700</v>
-      </c>
-      <c r="D80" s="46"/>
-      <c r="E80" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B81" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C81" s="45">
-        <f>C77*0.02</f>
-        <v>1800</v>
-      </c>
-      <c r="D81" s="46"/>
-      <c r="E81" s="35">
-        <v>2</v>
-      </c>
+      <c r="C64" s="51">
+        <f>J62</f>
+        <v>110400.97764374498</v>
+      </c>
+      <c r="D64" s="52"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="10">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C64:D64"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -2803,14 +2486,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2851,24 +2526,24 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
